--- a/GEKI/GEKI_要件定義書_v0.3.xlsx
+++ b/GEKI/GEKI_要件定義書_v0.3.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -663,20 +663,6 @@
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>■ サマリ（v0.3時点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>・機能要件 48件（Must 38／Should 10）・画面 15・非機能要件 18・確認事項 17件（うち★6件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>・新規：API 7本（案）・テーブル 5（案）・エラーコード 10・計測イベント 14・テスト観点 24・リスク 8・FAQ 10</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3579,6 +3565,23 @@
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>詳細設計フェーズへの橋渡しとして大幅拡充：画面遷移図／コードライフサイクル／API設計案／データモデル案／エラーコード体系／計測設計／テスト観点／リスク一覧／FAQドラフト／用語集を追加。FR 6件追加（FR-107, FR-207, FR-306改, FR-409, FR-410, FR-506, FR-606）。プロトタイプ v0.2 対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>0.3.1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>キャラクターダンス演出（FR-411）を追加。3Dモデル制作をスコープOUTに明記し、2.5D表現（レイヤーアニメ）を推奨方式として定義。プロトタイプ v0.2.1 で実演</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3866,17 +3869,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>販売</t>
+          <t>アセット</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>カードのEC構築・決済・在庫・物流</t>
+          <t>3Dキャラクターモデルの制作・リギング</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>MDチーム側の想定。要確認</t>
+          <t>企画書 p.9「映像は2Dビューでの制作」に準拠。ダンス演出は2Dパーツの2.5D表現で実現（FR-411）</t>
         </is>
       </c>
     </row>
@@ -3888,17 +3891,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>会員</t>
+          <t>販売</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>会員登録・ID/PW認証・メール配信基盤</t>
+          <t>カードのEC構築・決済・在庫・物流</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>2A決定によりログインは実装しない</t>
+          <t>MDチーム側の想定。要確認</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3913,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>システム</t>
+          <t>会員</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>端末紐付け管理・他端末制御・紐付け解除フロー</t>
+          <t>会員登録・ID/PW認証・メール配信基盤</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>2A決定により不要。設計を大幅に簡素化できる</t>
+          <t>2A決定によりログインは実装しない</t>
         </is>
       </c>
     </row>
@@ -3932,17 +3935,17 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>システム</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>提供期間（3ヶ月）を超える恒久運用・サーバー継続稼働</t>
+          <t>端末紐付け管理・他端末制御・紐付け解除フロー</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>終了後1ヶ月の保守のみ</t>
+          <t>2A決定により不要。設計を大幅に簡素化できる</t>
         </is>
       </c>
     </row>
@@ -3954,39 +3957,39 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>多言語</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>日本語以外の言語対応</t>
+          <t>提供期間（3ヶ月）を超える恒久運用・サーバー継続稼働</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>要確認：海外ファン向け需要</t>
+          <t>終了後1ヶ月の保守のみ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>販促</t>
+          <t>多言語</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>リアルイベント連動・店頭施策との接続</t>
+          <t>日本語以外の言語対応</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>実施有無が未定</t>
+          <t>要確認：海外ファン向け需要</t>
         </is>
       </c>
     </row>
@@ -3998,15 +4001,37 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>販促</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>リアルイベント連動・店頭施策との接続</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>実施有無が未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>機能</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>全カードコンプリート時の特典・限定演出</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>施策として検討余地あり（CQ-11と連動／FR-506をShouldで仮置き）</t>
         </is>
@@ -4023,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5387,44 +5412,44 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>FR-501</t>
+          <t>FR-411</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>リザルト</t>
+          <t>リズムゲーム</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>リザルト表示</t>
+          <t>キャラクターダンス演出</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>スコア・コンボ・ランク（S/A/B/C等）を表示する</t>
+          <t>着せ替え結果を反映したキャラクターが楽曲のBPMに同期してダンスする。判定（PERFECT等）・コンボ・曲展開（サビ）に応じて振付と演出強度が変化する</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>SC-10</t>
+          <t>SC-09</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>企画書 p.6 フロー⑧</t>
+          <t>【v0.3.1新規】企画書 p.9 の「映像は2Dビューでの制作」方針に整合する2.5D表現（2Dパーツのレイヤーアニメ＋擬似奥行き）を推奨。フル3Dモデル制作・リギングはスコープ外（§2）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>FR-502</t>
+          <t>FR-501</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -5434,12 +5459,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>シェア画像生成</t>
+          <t>リザルト表示</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>着せ替え結果とスコアを合成したシェア用画像を生成する</t>
+          <t>スコア・コンボ・ランク（S/A/B/C等）を表示する</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -5449,19 +5474,19 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>SC-11</t>
+          <t>SC-10</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>権利表記の要否は CQ-14</t>
+          <t>企画書 p.6 フロー⑧</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>FR-503</t>
+          <t>FR-502</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -5471,12 +5496,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>SNSシェア</t>
+          <t>シェア画像生成</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>X／Instagram／TikTokへのシェア導線を提供し、規定ハッシュタグを付与する</t>
+          <t>着せ替え結果とスコアを合成したシェア用画像を生成する</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -5491,14 +5516,14 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>＃ラブベリ ＃ちゃんみな（企画書 p.6）</t>
+          <t>権利表記の要否は CQ-14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>FR-504</t>
+          <t>FR-503</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -5508,12 +5533,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>回遊導線</t>
+          <t>SNSシェア</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>「もう一度プレイ」「別のカードを読み込む」「サイトTOPへ戻る」の導線を提供する</t>
+          <t>X／Instagram／TikTokへのシェア導線を提供し、規定ハッシュタグを付与する</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -5523,19 +5548,19 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>SC-10</t>
+          <t>SC-11</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>企画書 p.6 回遊導線</t>
+          <t>＃ラブベリ ＃ちゃんみな（企画書 p.6）</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>FR-505</t>
+          <t>FR-504</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -5545,34 +5570,34 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>ハイスコア保持</t>
+          <t>回遊導線</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>楽曲別のハイスコアを端末単位で保持・表示する</t>
+          <t>「もう一度プレイ」「別のカードを読み込む」「サイトTOPへ戻る」の導線を提供する</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>SC-08,SC-10</t>
+          <t>SC-10</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>全体ランキングは Could</t>
+          <t>企画書 p.6 回遊導線</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>FR-506</t>
+          <t>FR-505</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -5582,12 +5607,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>コンプリート演出</t>
+          <t>ハイスコア保持</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>全17種コンプリート時に特別演出・特典表示を行う</t>
+          <t>楽曲別のハイスコアを端末単位で保持・表示する</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -5597,56 +5622,56 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>SC-06,SC-10</t>
+          <t>SC-08,SC-10</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>【v0.3新規】保留案件の受け皿として仮置き（CQ-11連動）</t>
+          <t>全体ランキングは Could</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>FR-601</t>
+          <t>FR-506</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>管理・運用</t>
+          <t>リザルト</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>コード発行</t>
+          <t>コンプリート演出</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>カード印刷用のシリアルコードを一括発行し、印刷会社へ渡すリストを出力する</t>
+          <t>全17種コンプリート時に特別演出・特典表示を行う</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>SC-15</t>
+          <t>SC-06,SC-10</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>WBS E-04／API-06</t>
+          <t>【v0.3新規】保留案件の受け皿として仮置き（CQ-11連動）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>FR-602</t>
+          <t>FR-601</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -5656,12 +5681,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>コード状態照会・失効</t>
+          <t>コード発行</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>コード単位で使用状態を照会し、必要に応じて失効・未使用への差戻しを行う</t>
+          <t>カード印刷用のシリアルコードを一括発行し、印刷会社へ渡すリストを出力する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -5676,14 +5701,14 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CS対応の実行手段／API-07</t>
+          <t>WBS E-04／API-06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>FR-603</t>
+          <t>FR-602</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -5693,17 +5718,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>実績集計</t>
+          <t>コード状態照会・失効</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>コード消化数・プレイ数・楽曲別プレイ数・コーデ完成率を集計表示する</t>
+          <t>コード単位で使用状態を照会し、必要に応じて失効・未使用への差戻しを行う</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -5713,14 +5738,14 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>WBS E-07</t>
+          <t>CS対応の実行手段／API-07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>FR-604</t>
+          <t>FR-603</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -5730,34 +5755,34 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>提供期間終了処理</t>
+          <t>実績集計</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>終了日時以降は新規登録・プレイを停止し、終了画面へ切り替える</t>
+          <t>コード消化数・プレイ数・楽曲別プレイ数・コーデ完成率を集計表示する</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>SC-14</t>
+          <t>SC-15</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>WBS G-08</t>
+          <t>WBS E-07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>FR-605</t>
+          <t>FR-604</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -5767,62 +5792,99 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>コード復旧フロー</t>
+          <t>提供期間終了処理</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>通信断等でプレイできないままコードが消費された申告に対し、CS経由でコードを未使用に差し戻せるようにする</t>
+          <t>終了日時以降は新規登録・プレイを停止し、終了画面へ切り替える</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>SC-15</t>
+          <t>SC-14</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>★要確定：救済の有無（CQ-03）</t>
+          <t>WBS G-08</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>FR-605</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>管理・運用</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>コード復旧フロー</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>通信断等でプレイできないままコードが消費された申告に対し、CS経由でコードを未使用に差し戻せるようにする</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>★要確定：救済の有無（CQ-03）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
           <t>FR-606</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>管理・運用</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>操作監査ログ</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>管理画面でのコード状態変更（失効・差戻し）は操作者・日時・理由を記録し、後から追跡できるようにする</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>【v0.3新規】CS救済を安全に運用するための前提</t>
         </is>

--- a/GEKI/GEKI_要件定義書_v0.3.xlsx
+++ b/GEKI/GEKI_要件定義書_v0.3.xlsx
@@ -3492,7 +3492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3582,6 +3582,23 @@
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>キャラクターダンス演出（FR-411）を追加。3Dモデル制作をスコープOUTに明記し、2.5D表現（レイヤーアニメ）を推奨方式として定義。プロトタイプ v0.2.1 で実演</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>0.3.2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>プロトタイプ v0.2.2：外部共有用にIP名・アーティスト名・楽曲名・©表記をマスキング（「着せ替えカードIP × アーティストX」「楽曲A/B/C」等の伏せ字に置換）。コード手入力にデモ用ダミーコード「AAAA」を追加（未読込カードを順に仮登録）。本書（要件定義書）は実名のまま</t>
         </is>
       </c>
     </row>
